--- a/TestData/executeTestData.xlsx
+++ b/TestData/executeTestData.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gaurav\Desktop\Claude\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Eclipse-Selenium 13-07-2024\eclipse-java\PlaywrightJava\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16524D6F-DC5A-4F7A-8520-AE09BC07E0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8227F48A-DEE5-4101-B22C-0C4495117C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TestCase" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
   <si>
     <t>Project Name</t>
   </si>
@@ -290,6 +290,27 @@
   </si>
   <si>
     <t>Verify user entered ticket details in confirm booking page and click on the "Confirm Booking" button</t>
+  </si>
+  <si>
+    <t>Login,Logout</t>
+  </si>
+  <si>
+    <t>Keywords</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Login,FeaturedEvent,Logout</t>
+  </si>
+  <si>
+    <t>Login,FeaturedEvent,ConfirmBooking,Logout</t>
+  </si>
+  <si>
+    <t>Login,FeaturedEvent,ConfirmBooking,CancelBooking,Logout</t>
+  </si>
+  <si>
+    <t>Login,CreateEvent,Logout</t>
   </si>
 </sst>
 </file>
@@ -653,21 +674,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I25"/>
+  <dimension ref="A2:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="85.77734375" customWidth="1"/>
-    <col min="5" max="5" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.44140625" customWidth="1"/>
-    <col min="7" max="7" width="34.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" customWidth="1"/>
+    <col min="8" max="8" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -678,8 +700,9 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -690,8 +713,9 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -700,8 +724,9 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -712,8 +737,9 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -724,8 +750,9 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -736,8 +763,9 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -746,16 +774,18 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -769,22 +799,25 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="8" t="s">
         <v>21</v>
@@ -793,24 +826,26 @@
       <c r="D11" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="2"/>
+      <c r="G11" s="1"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="2"/>
+      <c r="G12" s="1"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>1</v>
       </c>
@@ -823,23 +858,26 @@
       <c r="D13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="144" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>2</v>
       </c>
@@ -852,23 +890,26 @@
       <c r="D14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="144" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>3</v>
       </c>
@@ -881,23 +922,26 @@
       <c r="D15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>4</v>
       </c>
@@ -910,23 +954,26 @@
       <c r="D16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="216" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
@@ -935,23 +982,26 @@
       <c r="D17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>5</v>
       </c>
@@ -964,21 +1014,24 @@
       <c r="D18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="2"/>
+      <c r="H18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>6</v>
       </c>
@@ -991,32 +1044,36 @@
       <c r="D19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="2"/>
       <c r="C20" s="3"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
@@ -1025,13 +1082,14 @@
       <c r="D21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" ht="288" x14ac:dyDescent="0.3">
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="288" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>7</v>
       </c>
@@ -1045,20 +1103,21 @@
         <v>61</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="2"/>
+      <c r="G22" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="I22" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>8</v>
       </c>
@@ -1072,25 +1131,26 @@
         <v>66</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="2"/>
+      <c r="G23" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="J23" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
         <v>14</v>
       </c>
